--- a/public/templates/champion-import-physical-tests.xlsx
+++ b/public/templates/champion-import-physical-tests.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Фізичні тести" sheetId="1" r:id="Rfc6ae6b027644668"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Інструкція" sheetId="2" r:id="R2a607a35024f476f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Умови тестування" sheetId="3" r:id="Rc3aed3fd256d4fd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Фізичні тести" sheetId="1" r:id="Re66452c145cb432c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Інструкція" sheetId="2" r:id="R6be3afd304374ab0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Умови тестування" sheetId="3" r:id="R04ac921282b04689"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -860,7 +860,7 @@
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="98" t="str">
-        <x:v>ПРИКЛАД — U14A</x:v>
+        <x:v>ПРИКЛАД — U16A</x:v>
       </x:c>
       <x:c r="B7" s="98" t="str">
         <x:v>Шевченко Максим Ігорович</x:v>
@@ -883,7 +883,7 @@
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="98" t="str">
-        <x:v>ПРИКЛАД — U14A</x:v>
+        <x:v>ПРИКЛАД — U16A</x:v>
       </x:c>
       <x:c r="B8" s="98" t="str">
         <x:v>Шевченко Максим Ігорович</x:v>
@@ -906,7 +906,7 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="98" t="str">
-        <x:v>ПРИКЛАД — U14A</x:v>
+        <x:v>ПРИКЛАД — U16A</x:v>
       </x:c>
       <x:c r="B9" s="98" t="str">
         <x:v>Шевченко Максим Ігорович</x:v>
@@ -929,7 +929,7 @@
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="98" t="str">
-        <x:v>ПРИКЛАД — U14A</x:v>
+        <x:v>ПРИКЛАД — U16A</x:v>
       </x:c>
       <x:c r="B10" s="98" t="str">
         <x:v>Шевченко Максим Ігорович</x:v>
@@ -952,7 +952,7 @@
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="98" t="str">
-        <x:v>ПРИКЛАД — U14A</x:v>
+        <x:v>ПРИКЛАД — U16A</x:v>
       </x:c>
       <x:c r="B11" s="98" t="str">
         <x:v>Шевченко Максим Ігорович</x:v>
@@ -975,7 +975,7 @@
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="98" t="str">
-        <x:v>ПРИКЛАД — U14A</x:v>
+        <x:v>ПРИКЛАД — U16A</x:v>
       </x:c>
       <x:c r="B12" s="98" t="str">
         <x:v>Шевченко Максим Ігорович</x:v>
@@ -16906,7 +16906,7 @@
   </x:sheetData>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="A2:A5001">
-      <x:formula1>"U6,U7,U8A,U8B,U9A,U9B,U10A,U10B,U11A,U11B,U12A,U12B,U13A,U13B,U14A,U14B,U15A,U15B,Воротарі A,Воротарі B,Воротарі C"</x:formula1>
+      <x:formula1>"U6,U7,U8A,U8B,U9A,U9B,U10A,U10B,U11A,U11B,U12A,U12B,U13A,U13B,U14A,U14B,U15A,U15B,U16A,U16B,U17A,U17B,Воротарі A,Воротарі B,Воротарі C"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17070,7 +17070,7 @@
         <x:v>1.</x:v>
       </x:c>
       <x:c r="B15" s="70" t="str">
-        <x:v>Для U6–U12 є 4 тести та 5 полів результату; для U13–U15 — 4 тести та 6 полів.</x:v>
+        <x:v>Для U6–U12 є 4 тести та 5 полів результату; для U13–U17 — 4 тести та 6 полів.</x:v>
       </x:c>
       <x:c r="C15" s="70"/>
       <x:c r="D15" s="70"/>
